--- a/test_exel/Бюджет шаблон.xlsx
+++ b/test_exel/Бюджет шаблон.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test exel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_exel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4377AEB-1D58-4C8B-B29A-03142E906091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAFF4F8F-C799-485D-87F7-E4F12AB45DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="294" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="расчет" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">расчет!$A$9:$AG$56</definedName>
-    <definedName name="Длина_сделки">расчет!$K$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">расчет!$A$9:$AG$36</definedName>
+    <definedName name="Длина_сделки">расчет!$K$15</definedName>
   </definedNames>
   <calcPr calcId="191029" fullPrecision="0"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="77">
   <si>
     <t>По номенклатуре:</t>
   </si>
@@ -208,9 +208,6 @@
     <t>Итого по спецификации</t>
   </si>
   <si>
-    <t>№</t>
-  </si>
-  <si>
     <t>Итого по бюджету сделки</t>
   </si>
   <si>
@@ -218,6 +215,63 @@
   </si>
   <si>
     <t>Сумма НДС (начислено)</t>
+  </si>
+  <si>
+    <t>Выручка по контракту (без НДС)</t>
+  </si>
+  <si>
+    <t>Всего прямых затрат, в т.ч. (без НДС)</t>
+  </si>
+  <si>
+    <t>- стоимость контракта</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - стоимость конвертации (3,2%)</t>
+  </si>
+  <si>
+    <t>КНР</t>
+  </si>
+  <si>
+    <t>- таможенная пошлина (плановая)</t>
+  </si>
+  <si>
+    <t>- транспортные до границы РФ</t>
+  </si>
+  <si>
+    <t>- транспортные по РФ</t>
+  </si>
+  <si>
+    <t>ДА</t>
+  </si>
+  <si>
+    <t>НЕТ</t>
+  </si>
+  <si>
+    <t>РФ</t>
+  </si>
+  <si>
+    <t>КРЕДИТ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - сертификация</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - шеф-монтаж</t>
+  </si>
+  <si>
+    <t>БАНКОВСКАЯ ГАРАНТИЯ</t>
+  </si>
+  <si>
+    <t>- ПНР</t>
+  </si>
+  <si>
+    <t>Маржинальный доход (вклад на покрытие), руб</t>
+  </si>
+  <si>
+    <t>Скидка, %</t>
+  </si>
+  <si>
+    <t>Маржинальный доход , %</t>
   </si>
 </sst>
 </file>
@@ -3029,7 +3083,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3125,9 +3179,6 @@
     <xf numFmtId="1" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="32" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="1" fontId="32" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -3222,9 +3273,6 @@
     <xf numFmtId="184" fontId="32" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3235,9 +3283,6 @@
     <xf numFmtId="1" fontId="32" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="32" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="175" fontId="32" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3291,9 +3336,6 @@
     <xf numFmtId="1" fontId="32" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="32" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="183" fontId="38" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3362,12 +3404,6 @@
     </xf>
     <xf numFmtId="0" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3419,75 +3455,103 @@
     <xf numFmtId="175" fontId="32" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="32" fillId="2" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="175" fontId="32" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="32" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="32" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="32" fillId="2" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="32" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="32" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="32" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="32" fillId="4" borderId="14" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1662">
@@ -5154,7 +5218,13 @@
     <cellStyle name="常规 8 2" xfId="1463" xr:uid="{00000000-0005-0000-0000-00007C060000}"/>
     <cellStyle name="常规 9" xfId="6" xr:uid="{00000000-0005-0000-0000-00007D060000}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -5492,7 +5562,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:AG67"/>
+  <dimension ref="A1:AG47"/>
   <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="11.45" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="0.33203125" style="1" customWidth="1"/>
@@ -5508,8 +5578,8 @@
     <col min="13" max="13" width="19.6640625" style="1" customWidth="1"/>
     <col min="14" max="14" width="16.1640625" style="1" customWidth="1"/>
     <col min="15" max="15" width="28.5" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.1640625" style="104" customWidth="1"/>
-    <col min="17" max="17" width="16.6640625" style="104" customWidth="1"/>
+    <col min="16" max="16" width="11.1640625" style="100" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" style="100" customWidth="1"/>
     <col min="18" max="18" width="16.6640625" style="8" customWidth="1"/>
     <col min="19" max="19" width="15.6640625" style="8" customWidth="1"/>
     <col min="20" max="20" width="16.1640625" style="8" customWidth="1"/>
@@ -5526,22 +5596,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" s="1" customFormat="1" ht="32.1" customHeight="1">
-      <c r="B1" s="139" t="s">
+      <c r="B1" s="156" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="157"/>
+      <c r="K1" s="157"/>
+      <c r="L1" s="157"/>
+      <c r="M1" s="157"/>
+      <c r="N1" s="157"/>
+      <c r="O1" s="158"/>
     </row>
     <row r="2" spans="1:30" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="B2" s="2"/>
@@ -5554,11 +5624,11 @@
       <c r="H2" s="5"/>
       <c r="I2" s="2"/>
       <c r="J2" s="6"/>
-      <c r="V2" s="142"/>
-      <c r="W2" s="142"/>
-      <c r="X2" s="142"/>
-      <c r="Y2" s="142"/>
-      <c r="Z2" s="142"/>
+      <c r="V2" s="149"/>
+      <c r="W2" s="149"/>
+      <c r="X2" s="149"/>
+      <c r="Y2" s="149"/>
+      <c r="Z2" s="149"/>
     </row>
     <row r="3" spans="1:30" ht="15" customHeight="1">
       <c r="B3" s="2"/>
@@ -5580,11 +5650,11 @@
       <c r="O3" s="5"/>
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
-      <c r="V3" s="142"/>
-      <c r="W3" s="142"/>
-      <c r="X3" s="142"/>
-      <c r="Y3" s="142"/>
-      <c r="Z3" s="142"/>
+      <c r="V3" s="149"/>
+      <c r="W3" s="149"/>
+      <c r="X3" s="149"/>
+      <c r="Y3" s="149"/>
+      <c r="Z3" s="149"/>
     </row>
     <row r="4" spans="1:30" ht="39.75" customHeight="1">
       <c r="B4" s="9"/>
@@ -5602,17 +5672,17 @@
       <c r="M4" s="2"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
-      <c r="P4" s="144"/>
-      <c r="Q4" s="144"/>
-      <c r="R4" s="144"/>
-      <c r="S4" s="144"/>
-      <c r="T4" s="144"/>
-      <c r="U4" s="144"/>
-      <c r="V4" s="142"/>
-      <c r="W4" s="142"/>
-      <c r="X4" s="142"/>
-      <c r="Y4" s="142"/>
-      <c r="Z4" s="142"/>
+      <c r="P4" s="159"/>
+      <c r="Q4" s="160"/>
+      <c r="R4" s="160"/>
+      <c r="S4" s="160"/>
+      <c r="T4" s="160"/>
+      <c r="U4" s="161"/>
+      <c r="V4" s="149"/>
+      <c r="W4" s="149"/>
+      <c r="X4" s="149"/>
+      <c r="Y4" s="149"/>
+      <c r="Z4" s="149"/>
     </row>
     <row r="5" spans="1:30" ht="15" customHeight="1">
       <c r="B5" s="12"/>
@@ -5637,18 +5707,18 @@
       <c r="S5" s="16"/>
       <c r="T5" s="16"/>
       <c r="U5" s="16"/>
-      <c r="V5" s="142"/>
-      <c r="W5" s="142"/>
-      <c r="X5" s="142"/>
-      <c r="Y5" s="142"/>
-      <c r="Z5" s="142"/>
+      <c r="V5" s="149"/>
+      <c r="W5" s="149"/>
+      <c r="X5" s="149"/>
+      <c r="Y5" s="149"/>
+      <c r="Z5" s="149"/>
     </row>
     <row r="6" spans="1:30" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="17"/>
-      <c r="B6" s="146" t="s">
+      <c r="B6" s="152" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="146"/>
+      <c r="C6" s="152"/>
       <c r="D6" s="18"/>
       <c r="E6" s="19"/>
       <c r="F6" s="20"/>
@@ -5661,43 +5731,43 @@
       <c r="M6" s="20"/>
       <c r="N6" s="20"/>
       <c r="O6" s="20"/>
-      <c r="V6" s="143"/>
-      <c r="W6" s="143"/>
-      <c r="X6" s="143"/>
-      <c r="Y6" s="143"/>
-      <c r="Z6" s="143"/>
+      <c r="V6" s="150"/>
+      <c r="W6" s="150"/>
+      <c r="X6" s="150"/>
+      <c r="Y6" s="150"/>
+      <c r="Z6" s="150"/>
     </row>
     <row r="7" spans="1:30" ht="15" customHeight="1">
       <c r="A7" s="15"/>
-      <c r="B7" s="149" t="s">
+      <c r="B7" s="155" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="140"/>
-      <c r="D7" s="140"/>
-      <c r="E7" s="140"/>
-      <c r="F7" s="140"/>
-      <c r="G7" s="140"/>
-      <c r="H7" s="140"/>
-      <c r="I7" s="140"/>
-      <c r="J7" s="141"/>
-      <c r="K7" s="140" t="s">
+      <c r="C7" s="147"/>
+      <c r="D7" s="147"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="147"/>
+      <c r="G7" s="147"/>
+      <c r="H7" s="147"/>
+      <c r="I7" s="147"/>
+      <c r="J7" s="148"/>
+      <c r="K7" s="147" t="s">
         <v>2</v>
       </c>
-      <c r="L7" s="140"/>
-      <c r="M7" s="140"/>
-      <c r="N7" s="140"/>
-      <c r="O7" s="140"/>
-      <c r="P7" s="140"/>
-      <c r="Q7" s="140"/>
-      <c r="R7" s="140"/>
-      <c r="S7" s="140"/>
-      <c r="T7" s="140"/>
-      <c r="U7" s="140"/>
-      <c r="V7" s="140"/>
-      <c r="W7" s="140"/>
-      <c r="X7" s="140"/>
-      <c r="Y7" s="140"/>
-      <c r="Z7" s="141"/>
+      <c r="L7" s="147"/>
+      <c r="M7" s="147"/>
+      <c r="N7" s="147"/>
+      <c r="O7" s="147"/>
+      <c r="P7" s="147"/>
+      <c r="Q7" s="147"/>
+      <c r="R7" s="147"/>
+      <c r="S7" s="147"/>
+      <c r="T7" s="147"/>
+      <c r="U7" s="147"/>
+      <c r="V7" s="147"/>
+      <c r="W7" s="147"/>
+      <c r="X7" s="147"/>
+      <c r="Y7" s="147"/>
+      <c r="Z7" s="148"/>
     </row>
     <row r="8" spans="1:30" s="22" customFormat="1" ht="54.75" customHeight="1">
       <c r="A8" s="21"/>
@@ -5767,10 +5837,10 @@
       <c r="W8" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="X8" s="147" t="s">
+      <c r="X8" s="153" t="s">
         <v>23</v>
       </c>
-      <c r="Y8" s="148"/>
+      <c r="Y8" s="154"/>
       <c r="Z8" s="25" t="s">
         <v>22</v>
       </c>
@@ -5779,1901 +5849,952 @@
       <c r="AC8" s="30"/>
       <c r="AD8" s="21"/>
     </row>
-    <row r="9" spans="1:30" s="42" customFormat="1" ht="19.5" customHeight="1">
+    <row r="9" spans="1:30" s="41" customFormat="1" ht="19.5" customHeight="1">
       <c r="A9" s="31"/>
-      <c r="B9" s="145">
+      <c r="B9" s="151">
         <v>1</v>
       </c>
-      <c r="C9" s="145"/>
+      <c r="C9" s="151"/>
       <c r="D9" s="32"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33">
+      <c r="E9" s="140"/>
+      <c r="F9" s="140">
         <v>2</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="140">
         <v>3</v>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="33">
         <v>4</v>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="33">
         <v>5</v>
       </c>
-      <c r="J9" s="35"/>
-      <c r="K9" s="34">
+      <c r="J9" s="34"/>
+      <c r="K9" s="33">
         <v>6</v>
       </c>
-      <c r="L9" s="36">
+      <c r="L9" s="35">
         <v>7</v>
       </c>
-      <c r="M9" s="34">
+      <c r="M9" s="33">
         <v>8</v>
       </c>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34">
+      <c r="N9" s="33"/>
+      <c r="O9" s="33">
         <v>9</v>
       </c>
-      <c r="P9" s="34">
+      <c r="P9" s="33">
         <v>10</v>
       </c>
-      <c r="Q9" s="37">
+      <c r="Q9" s="36">
         <v>11</v>
       </c>
-      <c r="R9" s="37">
+      <c r="R9" s="36">
         <v>12</v>
       </c>
-      <c r="S9" s="37">
+      <c r="S9" s="36">
         <v>13</v>
       </c>
-      <c r="T9" s="37">
+      <c r="T9" s="36">
         <v>14</v>
       </c>
-      <c r="U9" s="38">
+      <c r="U9" s="37">
         <v>15</v>
       </c>
-      <c r="V9" s="38"/>
-      <c r="W9" s="38">
+      <c r="V9" s="37"/>
+      <c r="W9" s="37">
         <v>16</v>
       </c>
-      <c r="X9" s="38">
+      <c r="X9" s="37">
         <v>17</v>
       </c>
-      <c r="Y9" s="38"/>
-      <c r="Z9" s="38">
+      <c r="Y9" s="37"/>
+      <c r="Z9" s="37">
         <v>19</v>
       </c>
-      <c r="AA9" s="39"/>
-      <c r="AB9" s="39"/>
-      <c r="AC9" s="40"/>
-      <c r="AD9" s="41"/>
+      <c r="AA9" s="38"/>
+      <c r="AB9" s="38"/>
+      <c r="AC9" s="39"/>
+      <c r="AD9" s="40"/>
     </row>
-    <row r="10" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A10" s="43"/>
-      <c r="B10" s="44">
+    <row r="10" spans="1:30" s="64" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A10" s="42"/>
+      <c r="B10" s="43">
         <v>1</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="48" t="s">
+      <c r="C10" s="44"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="49"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50">
+      <c r="G10" s="48"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49">
         <f>G10*H10</f>
         <v>0</v>
       </c>
-      <c r="J10" s="51">
+      <c r="J10" s="50">
         <f>I10*14</f>
         <v>0</v>
       </c>
-      <c r="K10" s="52" t="s">
+      <c r="K10" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="L10" s="53">
+      <c r="L10" s="52">
         <f>G10</f>
         <v>0</v>
       </c>
-      <c r="M10" s="54"/>
-      <c r="N10" s="55" t="e">
+      <c r="M10" s="53"/>
+      <c r="N10" s="54" t="e">
         <f>M10/P10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O10" s="56">
+      <c r="O10" s="55">
         <f>M10*L10</f>
         <v>0</v>
       </c>
-      <c r="P10" s="57"/>
-      <c r="Q10" s="58">
+      <c r="P10" s="56"/>
+      <c r="Q10" s="57">
         <f>P10*L10</f>
         <v>0</v>
       </c>
-      <c r="R10" s="111" t="e">
-        <f>$U$34/$Q$31*P10/12*0.3</f>
+      <c r="R10" s="107" t="e">
+        <f>$U$14/$Q$11*P10/12*0.3</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S10" s="59" t="e">
+      <c r="S10" s="58" t="e">
         <f>R10*L10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T10" s="59" t="e">
-        <f>$U$34/$Q$31*P10/12*0.7</f>
+      <c r="T10" s="58" t="e">
+        <f>$U$14/$Q$11*P10/12*0.7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U10" s="59" t="e">
+      <c r="U10" s="58" t="e">
         <f>T10*L10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="V10" s="60" t="e">
+      <c r="V10" s="59" t="e">
         <f>H10/P10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="W10" s="55" t="e">
+      <c r="W10" s="54" t="e">
         <f>N10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X10" s="61" t="s">
+      <c r="X10" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="Y10" s="62" t="e">
+      <c r="Y10" s="61" t="e">
         <f>L10*(M10+R10)*X10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z10" s="63" t="e">
+      <c r="Z10" s="62" t="e">
         <f>(I10-O10-S10-U10-Y10-AA10-AC10-AB10)/I10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA10" s="64"/>
-      <c r="AB10" s="64"/>
-      <c r="AC10" s="64"/>
-      <c r="AD10" s="65"/>
+      <c r="AA10" s="63"/>
+      <c r="AB10" s="63"/>
+      <c r="AC10" s="63"/>
+      <c r="AD10" s="139"/>
     </row>
-    <row r="11" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A11" s="43"/>
-      <c r="B11" s="44">
-        <v>2</v>
-      </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="49"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50">
-        <f t="shared" ref="I11:I30" si="0">G11*H11</f>
+    <row r="11" spans="1:30" s="64" customFormat="1" ht="15" customHeight="1">
+      <c r="A11" s="42"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="146"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="49">
+        <f>SUM(I10:I10)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="51">
-        <f t="shared" ref="J11:J30" si="1">I11*14</f>
+      <c r="J11" s="69"/>
+      <c r="K11" s="70"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="72"/>
+      <c r="N11" s="73"/>
+      <c r="O11" s="49">
+        <f>SUM(O10:O10)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L11" s="53">
-        <f t="shared" ref="L11:L30" si="2">G11</f>
+      <c r="P11" s="74"/>
+      <c r="Q11" s="75">
+        <f>SUM(Q10:Q10)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="54"/>
-      <c r="N11" s="55" t="e">
-        <f t="shared" ref="N11:N30" si="3">M11/P11</f>
+      <c r="R11" s="76"/>
+      <c r="S11" s="49" t="e">
+        <f>SUM(S10:S10)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O11" s="56">
-        <f t="shared" ref="O11:O30" si="4">M11*L11</f>
+      <c r="T11" s="77"/>
+      <c r="U11" s="77" t="e">
+        <f>SUM(U10:U10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V11" s="78"/>
+      <c r="W11" s="79"/>
+      <c r="X11" s="80" t="e">
+        <f>AVERAGE(X10:X10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y11" s="49" t="e">
+        <f>SUM(Y10:Y10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z11" s="81" t="e">
+        <f>(I11-O11-S11-U11-Y11-AA11-AC11-AB11)/I11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA11" s="63"/>
+      <c r="AB11" s="63"/>
+      <c r="AC11" s="63"/>
+      <c r="AD11" s="8"/>
+    </row>
+    <row r="12" spans="1:30" s="64" customFormat="1" ht="15" customHeight="1">
+      <c r="A12" s="42"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="145"/>
+      <c r="H12" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="49">
+        <f>I11*1.2</f>
         <v>0</v>
       </c>
-      <c r="P11" s="57"/>
-      <c r="Q11" s="58">
-        <f t="shared" ref="Q11:Q30" si="5">P11*L11</f>
+      <c r="J12" s="85"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="86"/>
+      <c r="M12" s="87"/>
+      <c r="N12" s="87"/>
+      <c r="O12" s="88"/>
+      <c r="P12" s="89"/>
+      <c r="Q12" s="90"/>
+      <c r="R12" s="91"/>
+      <c r="S12" s="92"/>
+      <c r="T12" s="93"/>
+      <c r="U12" s="94"/>
+      <c r="V12" s="78"/>
+      <c r="W12" s="79"/>
+      <c r="X12" s="95"/>
+      <c r="Y12" s="96"/>
+      <c r="Z12" s="97"/>
+      <c r="AC12" s="98"/>
+      <c r="AD12" s="139"/>
+    </row>
+    <row r="13" spans="1:30" s="1" customFormat="1" ht="14.1" customHeight="1">
+      <c r="A13" s="143" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="141" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="142"/>
+      <c r="D13" s="138"/>
+      <c r="E13" s="138"/>
+      <c r="F13" s="144"/>
+      <c r="G13" s="144"/>
+      <c r="H13" s="144"/>
+      <c r="K13" s="100"/>
+      <c r="L13" s="100"/>
+      <c r="P13"/>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
+      <c r="W13"/>
+      <c r="X13"/>
+      <c r="Y13"/>
+      <c r="Z13"/>
+      <c r="AA13"/>
+      <c r="AD13" s="15"/>
+    </row>
+    <row r="14" spans="1:30" ht="14.1" customHeight="1">
+      <c r="A14" s="143" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="108" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="109"/>
+      <c r="D14" s="109"/>
+      <c r="E14" s="109"/>
+      <c r="F14" s="109"/>
+      <c r="G14" s="109"/>
+      <c r="H14" s="109"/>
+      <c r="I14" s="110"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="100"/>
+      <c r="L14" s="100"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="115"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+      <c r="R14"/>
+      <c r="S14"/>
+      <c r="T14"/>
+      <c r="U14"/>
+      <c r="V14"/>
+      <c r="W14"/>
+      <c r="X14"/>
+      <c r="Y14"/>
+      <c r="Z14"/>
+      <c r="AA14"/>
+    </row>
+    <row r="15" spans="1:30" s="1" customFormat="1" ht="14.1" customHeight="1">
+      <c r="A15" s="99" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="108" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="109"/>
+      <c r="D15" s="109"/>
+      <c r="E15" s="109"/>
+      <c r="F15" s="109"/>
+      <c r="G15" s="109"/>
+      <c r="H15" s="109"/>
+      <c r="I15" s="113">
+        <v>150</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="100">
+        <f>I15+I16</f>
+        <v>180</v>
+      </c>
+      <c r="L15" s="100"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+      <c r="R15"/>
+      <c r="S15"/>
+      <c r="T15"/>
+      <c r="U15"/>
+      <c r="V15"/>
+      <c r="W15"/>
+      <c r="X15"/>
+      <c r="Y15"/>
+      <c r="Z15"/>
+      <c r="AA15"/>
+    </row>
+    <row r="16" spans="1:30" s="41" customFormat="1" ht="14.1" customHeight="1">
+      <c r="A16" s="99" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="111" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="112"/>
+      <c r="D16" s="112"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="112"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="114">
+        <v>30</v>
+      </c>
+      <c r="J16" s="116"/>
+      <c r="K16" s="100"/>
+      <c r="L16" s="100"/>
+      <c r="N16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O16" s="117">
+        <f>I11*14</f>
         <v>0</v>
       </c>
-      <c r="R11" s="111" t="e">
-        <f t="shared" ref="R11:R30" si="6">$U$34/$Q$31*P11/12*0.3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S11" s="59" t="e">
-        <f t="shared" ref="S11:S30" si="7">R11*L11</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T11" s="59" t="e">
-        <f t="shared" ref="T11:T30" si="8">$U$34/$Q$31*P11/12*0.7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U11" s="59" t="e">
-        <f t="shared" ref="U11:U30" si="9">T11*L11</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V11" s="60" t="e">
-        <f t="shared" ref="V11:V30" si="10">H11/P11</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W11" s="55" t="e">
-        <f t="shared" ref="W11:W30" si="11">N11</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X11" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y11" s="62" t="e">
-        <f t="shared" ref="Y11:Y30" si="12">L11*(M11+R11)*X11</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z11" s="63" t="e">
-        <f t="shared" ref="Z11:Z30" si="13">(I11-O11-S11-U11-Y11-AA11-AC11-AB11)/I11</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA11" s="64"/>
-      <c r="AB11" s="64"/>
-      <c r="AC11" s="64"/>
-      <c r="AD11" s="112"/>
+      <c r="P16"/>
+      <c r="Q16"/>
+      <c r="R16"/>
+      <c r="S16"/>
+      <c r="T16"/>
+      <c r="U16"/>
+      <c r="V16"/>
+      <c r="W16"/>
+      <c r="X16"/>
+      <c r="Y16"/>
+      <c r="Z16"/>
+      <c r="AA16"/>
     </row>
-    <row r="12" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A12" s="43"/>
-      <c r="B12" s="44">
-        <v>3</v>
-      </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="49"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50">
-        <f t="shared" si="0"/>
+    <row r="17" spans="1:32" ht="14.1" customHeight="1">
+      <c r="A17" s="99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="124" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="125"/>
+      <c r="D17" s="125"/>
+      <c r="E17" s="125"/>
+      <c r="F17" s="125"/>
+      <c r="G17" s="125"/>
+      <c r="H17" s="126"/>
+      <c r="I17" s="118"/>
+      <c r="J17" s="119"/>
+      <c r="K17" s="100"/>
+      <c r="L17" s="100"/>
+      <c r="N17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O17" s="117">
+        <f>I12*14</f>
         <v>0</v>
       </c>
-      <c r="J12" s="51">
-        <f t="shared" si="1"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+      <c r="R17"/>
+      <c r="S17"/>
+      <c r="T17"/>
+      <c r="U17"/>
+      <c r="V17"/>
+      <c r="W17"/>
+      <c r="X17"/>
+      <c r="Y17"/>
+      <c r="Z17"/>
+      <c r="AA17"/>
+    </row>
+    <row r="18" spans="1:32" ht="14.1" customHeight="1">
+      <c r="A18" s="99" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="124" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="125"/>
+      <c r="D18" s="125"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="125"/>
+      <c r="H18" s="126"/>
+      <c r="I18" s="120"/>
+      <c r="J18" s="121"/>
+      <c r="K18" s="100"/>
+      <c r="L18" s="100"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+      <c r="R18"/>
+      <c r="S18"/>
+      <c r="T18"/>
+      <c r="U18"/>
+      <c r="V18"/>
+      <c r="W18"/>
+      <c r="X18"/>
+      <c r="Y18"/>
+      <c r="Z18"/>
+      <c r="AA18"/>
+    </row>
+    <row r="19" spans="1:32" ht="14.1" customHeight="1">
+      <c r="A19" s="99" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="124" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="125"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="125"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="126"/>
+      <c r="I19" s="122">
+        <f>I11</f>
         <v>0</v>
       </c>
-      <c r="K12" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L12" s="53">
-        <f t="shared" si="2"/>
+      <c r="J19" s="123"/>
+      <c r="K19" s="100"/>
+      <c r="L19" s="100"/>
+      <c r="M19" s="8"/>
+      <c r="P19"/>
+      <c r="Q19"/>
+      <c r="R19"/>
+      <c r="S19"/>
+      <c r="T19"/>
+      <c r="U19"/>
+      <c r="V19"/>
+      <c r="W19"/>
+      <c r="X19"/>
+      <c r="Y19"/>
+      <c r="Z19"/>
+      <c r="AA19"/>
+    </row>
+    <row r="20" spans="1:32" s="1" customFormat="1" ht="12" customHeight="1">
+      <c r="A20" s="99" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="124"/>
+      <c r="C20" s="125"/>
+      <c r="D20" s="125"/>
+      <c r="E20" s="125"/>
+      <c r="F20" s="125"/>
+      <c r="G20" s="125"/>
+      <c r="H20" s="126"/>
+      <c r="I20" s="122"/>
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20"/>
+      <c r="M20"/>
+      <c r="N20"/>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+      <c r="R20"/>
+      <c r="S20"/>
+      <c r="T20"/>
+      <c r="U20"/>
+      <c r="V20"/>
+      <c r="W20"/>
+      <c r="X20"/>
+      <c r="Y20"/>
+      <c r="Z20"/>
+      <c r="AA20"/>
+    </row>
+    <row r="21" spans="1:32" s="1" customFormat="1" ht="12" customHeight="1">
+      <c r="A21" s="99" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="124"/>
+      <c r="C21" s="125"/>
+      <c r="D21" s="125"/>
+      <c r="E21" s="125"/>
+      <c r="F21" s="125"/>
+      <c r="G21" s="125"/>
+      <c r="H21" s="126"/>
+      <c r="I21" s="122"/>
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+      <c r="R21"/>
+      <c r="S21"/>
+      <c r="T21"/>
+      <c r="U21"/>
+      <c r="V21"/>
+      <c r="W21"/>
+      <c r="X21"/>
+      <c r="Y21"/>
+      <c r="Z21"/>
+      <c r="AA21"/>
+    </row>
+    <row r="22" spans="1:32" s="1" customFormat="1" ht="11.1" customHeight="1">
+      <c r="A22" s="99" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="124"/>
+      <c r="C22" s="125"/>
+      <c r="D22" s="125"/>
+      <c r="E22" s="125"/>
+      <c r="F22" s="125"/>
+      <c r="G22" s="125"/>
+      <c r="H22" s="126"/>
+      <c r="I22" s="122"/>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+      <c r="P22"/>
+      <c r="Q22"/>
+      <c r="R22"/>
+      <c r="S22"/>
+      <c r="T22"/>
+      <c r="U22"/>
+      <c r="V22"/>
+      <c r="W22"/>
+      <c r="X22"/>
+      <c r="Y22"/>
+      <c r="Z22"/>
+      <c r="AA22"/>
+    </row>
+    <row r="23" spans="1:32" s="104" customFormat="1" ht="15" customHeight="1">
+      <c r="A23" s="101" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="131" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="130"/>
+      <c r="D23" s="125"/>
+      <c r="E23" s="125"/>
+      <c r="F23" s="125"/>
+      <c r="G23" s="125"/>
+      <c r="H23" s="126"/>
+      <c r="I23" s="129"/>
+      <c r="J23"/>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+      <c r="R23"/>
+      <c r="S23"/>
+      <c r="T23"/>
+      <c r="U23"/>
+      <c r="V23"/>
+      <c r="W23"/>
+      <c r="X23"/>
+      <c r="Y23"/>
+      <c r="Z23"/>
+      <c r="AA23"/>
+    </row>
+    <row r="24" spans="1:32" s="102" customFormat="1" ht="15" customHeight="1">
+      <c r="A24" s="105"/>
+      <c r="B24" s="124" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="125"/>
+      <c r="D24" s="125"/>
+      <c r="E24" s="125"/>
+      <c r="F24" s="125"/>
+      <c r="G24" s="125"/>
+      <c r="H24" s="126"/>
+      <c r="I24" s="127">
+        <f>I12</f>
         <v>0</v>
       </c>
-      <c r="M12" s="54"/>
-      <c r="N12" s="55" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O12" s="56">
-        <f t="shared" si="4"/>
+      <c r="J24"/>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24"/>
+      <c r="P24"/>
+      <c r="Q24"/>
+      <c r="R24"/>
+      <c r="S24"/>
+      <c r="T24"/>
+      <c r="U24"/>
+      <c r="V24"/>
+      <c r="W24"/>
+      <c r="X24"/>
+      <c r="Y24"/>
+      <c r="Z24"/>
+      <c r="AA24"/>
+    </row>
+    <row r="25" spans="1:32" s="64" customFormat="1" ht="15" customHeight="1">
+      <c r="A25" s="42"/>
+      <c r="B25" s="124" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="125"/>
+      <c r="D25" s="125"/>
+      <c r="E25" s="125"/>
+      <c r="F25" s="125"/>
+      <c r="G25" s="125"/>
+      <c r="H25" s="126"/>
+      <c r="I25" s="128">
+        <f>I24/120*20</f>
         <v>0</v>
       </c>
-      <c r="P12" s="57"/>
-      <c r="Q12" s="58">
-        <f t="shared" si="5"/>
+      <c r="J25"/>
+      <c r="K25"/>
+      <c r="L25"/>
+      <c r="M25"/>
+      <c r="N25"/>
+      <c r="O25"/>
+      <c r="P25"/>
+      <c r="Q25"/>
+      <c r="R25"/>
+      <c r="S25"/>
+      <c r="T25"/>
+      <c r="U25"/>
+      <c r="V25"/>
+      <c r="W25"/>
+      <c r="X25"/>
+      <c r="Y25"/>
+      <c r="Z25"/>
+      <c r="AA25"/>
+    </row>
+    <row r="26" spans="1:32" s="100" customFormat="1" ht="15" customHeight="1">
+      <c r="A26" s="106"/>
+      <c r="B26" s="124" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="125"/>
+      <c r="D26" s="125"/>
+      <c r="E26" s="125"/>
+      <c r="F26" s="125"/>
+      <c r="G26" s="125"/>
+      <c r="H26" s="126"/>
+      <c r="I26" s="128">
+        <f>I24-I25</f>
         <v>0</v>
       </c>
-      <c r="R12" s="111" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S12" s="59" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T12" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U12" s="59" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V12" s="60" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W12" s="55" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X12" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y12" s="62" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z12" s="63" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA12" s="64"/>
-      <c r="AB12" s="64"/>
-      <c r="AC12" s="64"/>
-      <c r="AD12" s="112"/>
+      <c r="J26"/>
+      <c r="K26"/>
+      <c r="L26"/>
+      <c r="M26"/>
+      <c r="N26"/>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
+      <c r="R26"/>
+      <c r="S26"/>
+      <c r="T26"/>
+      <c r="U26"/>
+      <c r="V26"/>
+      <c r="W26"/>
+      <c r="X26"/>
+      <c r="Y26"/>
+      <c r="Z26"/>
+      <c r="AA26"/>
     </row>
-    <row r="13" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A13" s="43"/>
-      <c r="B13" s="44">
-        <v>4</v>
-      </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="49"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50">
-        <f t="shared" si="0"/>
+    <row r="27" spans="1:32" s="100" customFormat="1" ht="15" customHeight="1">
+      <c r="A27" s="106"/>
+      <c r="B27" s="124" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="125"/>
+      <c r="D27" s="125"/>
+      <c r="E27" s="125"/>
+      <c r="F27" s="125"/>
+      <c r="G27" s="125"/>
+      <c r="H27" s="126"/>
+      <c r="I27" s="128">
+        <f>SUM(I28:I37)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="51">
-        <f t="shared" si="1"/>
+      <c r="J27"/>
+      <c r="K27"/>
+      <c r="L27"/>
+      <c r="M27"/>
+      <c r="N27"/>
+      <c r="O27"/>
+      <c r="P27"/>
+      <c r="Q27"/>
+      <c r="R27"/>
+      <c r="S27"/>
+      <c r="T27"/>
+      <c r="U27"/>
+      <c r="V27"/>
+      <c r="W27"/>
+      <c r="X27"/>
+      <c r="Y27"/>
+      <c r="Z27"/>
+      <c r="AA27"/>
+    </row>
+    <row r="28" spans="1:32" s="100" customFormat="1" ht="15" customHeight="1">
+      <c r="A28" s="106"/>
+      <c r="B28" s="124" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="125"/>
+      <c r="D28" s="125"/>
+      <c r="E28" s="125"/>
+      <c r="F28" s="125"/>
+      <c r="G28" s="125"/>
+      <c r="H28" s="126"/>
+      <c r="I28" s="128">
+        <f>O11</f>
         <v>0</v>
       </c>
-      <c r="K13" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L13" s="53">
-        <f t="shared" si="2"/>
+      <c r="J28"/>
+      <c r="K28"/>
+      <c r="L28"/>
+      <c r="M28"/>
+      <c r="N28"/>
+      <c r="O28"/>
+      <c r="P28"/>
+      <c r="Q28"/>
+      <c r="R28"/>
+      <c r="S28"/>
+      <c r="T28"/>
+      <c r="U28"/>
+      <c r="V28"/>
+      <c r="W28"/>
+      <c r="X28"/>
+      <c r="Y28"/>
+      <c r="Z28"/>
+      <c r="AA28"/>
+    </row>
+    <row r="29" spans="1:32" s="100" customFormat="1" ht="15" customHeight="1">
+      <c r="A29" s="106"/>
+      <c r="B29" s="136" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="137"/>
+      <c r="D29" s="137"/>
+      <c r="E29" s="137"/>
+      <c r="F29" s="137"/>
+      <c r="G29" s="134"/>
+      <c r="H29" s="132" t="s">
+        <v>62</v>
+      </c>
+      <c r="I29" s="133">
+        <f>IF(H29=D43,I28*3.2%,0)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="54"/>
-      <c r="N13" s="55" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O13" s="56">
-        <f t="shared" si="4"/>
+      <c r="J29"/>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29"/>
+      <c r="P29"/>
+      <c r="Q29"/>
+      <c r="R29"/>
+      <c r="S29"/>
+      <c r="T29"/>
+      <c r="U29"/>
+      <c r="V29"/>
+      <c r="W29"/>
+      <c r="X29"/>
+      <c r="Y29"/>
+      <c r="Z29"/>
+      <c r="AA29"/>
+    </row>
+    <row r="30" spans="1:32" s="100" customFormat="1" ht="15" customHeight="1">
+      <c r="A30" s="106"/>
+      <c r="B30" s="124" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="125"/>
+      <c r="D30" s="125"/>
+      <c r="E30" s="125"/>
+      <c r="F30" s="125"/>
+      <c r="G30" s="125"/>
+      <c r="H30" s="126"/>
+      <c r="I30" s="128">
+        <f>AA11</f>
         <v>0</v>
       </c>
-      <c r="P13" s="57"/>
-      <c r="Q13" s="58">
-        <f t="shared" si="5"/>
+      <c r="J30"/>
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30"/>
+      <c r="O30"/>
+      <c r="P30"/>
+      <c r="Q30"/>
+      <c r="R30"/>
+      <c r="S30"/>
+      <c r="T30"/>
+      <c r="U30"/>
+      <c r="V30"/>
+      <c r="W30"/>
+      <c r="X30"/>
+      <c r="Y30"/>
+      <c r="Z30"/>
+      <c r="AA30"/>
+    </row>
+    <row r="31" spans="1:32" s="100" customFormat="1" ht="15" customHeight="1">
+      <c r="A31" s="106"/>
+      <c r="B31" s="135" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="125"/>
+      <c r="D31" s="125"/>
+      <c r="E31" s="125"/>
+      <c r="F31" s="125"/>
+      <c r="G31" s="125"/>
+      <c r="H31" s="126"/>
+      <c r="I31" s="128">
+        <f>AB11</f>
         <v>0</v>
       </c>
-      <c r="R13" s="111" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S13" s="59" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T13" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U13" s="59" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V13" s="60" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W13" s="55" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X13" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y13" s="62" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z13" s="63" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA13" s="64"/>
-      <c r="AB13" s="64"/>
-      <c r="AC13" s="64"/>
-      <c r="AD13" s="112"/>
+      <c r="J31"/>
+      <c r="K31"/>
+      <c r="L31"/>
+      <c r="M31"/>
+      <c r="N31"/>
+      <c r="O31"/>
+      <c r="P31"/>
+      <c r="Q31"/>
+      <c r="R31"/>
+      <c r="S31"/>
+      <c r="T31"/>
+      <c r="U31"/>
+      <c r="V31"/>
+      <c r="W31"/>
+      <c r="X31"/>
+      <c r="Y31"/>
+      <c r="Z31"/>
+      <c r="AA31"/>
+      <c r="AB31" s="103"/>
+      <c r="AC31" s="103"/>
+      <c r="AD31" s="103"/>
+      <c r="AE31" s="103"/>
+      <c r="AF31" s="103"/>
     </row>
-    <row r="14" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A14" s="43"/>
-      <c r="B14" s="44">
-        <v>5</v>
-      </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="49"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="50">
-        <f t="shared" si="0"/>
+    <row r="32" spans="1:32" s="100" customFormat="1" ht="15" customHeight="1">
+      <c r="A32" s="106"/>
+      <c r="B32" s="135" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="125"/>
+      <c r="D32" s="125"/>
+      <c r="E32" s="125"/>
+      <c r="F32" s="125"/>
+      <c r="G32" s="125"/>
+      <c r="H32" s="126"/>
+      <c r="I32" s="128">
+        <f>AC11</f>
         <v>0</v>
       </c>
-      <c r="J14" s="51">
-        <f t="shared" si="1"/>
+      <c r="J32"/>
+      <c r="K32"/>
+      <c r="L32"/>
+      <c r="M32"/>
+      <c r="N32"/>
+      <c r="O32"/>
+      <c r="P32"/>
+      <c r="Q32"/>
+      <c r="R32"/>
+      <c r="S32"/>
+      <c r="T32"/>
+      <c r="U32"/>
+      <c r="V32"/>
+      <c r="W32"/>
+      <c r="X32"/>
+      <c r="Y32"/>
+      <c r="Z32"/>
+      <c r="AA32"/>
+      <c r="AB32" s="103"/>
+      <c r="AC32" s="103"/>
+      <c r="AD32" s="103"/>
+      <c r="AE32" s="103"/>
+      <c r="AF32" s="103"/>
+    </row>
+    <row r="33" spans="1:33" s="100" customFormat="1" ht="15" customHeight="1">
+      <c r="A33" s="106"/>
+      <c r="B33" s="136" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="137"/>
+      <c r="D33" s="137"/>
+      <c r="E33" s="137"/>
+      <c r="F33" s="137"/>
+      <c r="G33" s="134"/>
+      <c r="H33" s="132" t="s">
+        <v>66</v>
+      </c>
+      <c r="I33" s="133">
+        <f>IF(H33="ДА",I28*16%/365*Длина_сделки,0)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L14" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="54"/>
-      <c r="N14" s="55" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O14" s="56">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P14" s="57"/>
-      <c r="Q14" s="58">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="111" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S14" s="59" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T14" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U14" s="59" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V14" s="60" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W14" s="55" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X14" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y14" s="62" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z14" s="63" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA14" s="64"/>
-      <c r="AB14" s="64"/>
-      <c r="AC14" s="64"/>
-      <c r="AD14" s="112"/>
-    </row>
-    <row r="15" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A15" s="43"/>
-      <c r="B15" s="44">
-        <v>6</v>
-      </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" s="49"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L15" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="54"/>
-      <c r="N15" s="55" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O15" s="56">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P15" s="57"/>
-      <c r="Q15" s="58">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R15" s="111" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S15" s="59" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T15" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U15" s="59" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V15" s="60" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W15" s="55" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X15" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y15" s="62" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z15" s="63" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA15" s="64"/>
-      <c r="AB15" s="64"/>
-      <c r="AC15" s="64"/>
-      <c r="AD15" s="112"/>
-    </row>
-    <row r="16" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A16" s="43"/>
-      <c r="B16" s="44">
-        <v>7</v>
-      </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L16" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="54"/>
-      <c r="N16" s="55" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O16" s="56">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="57"/>
-      <c r="Q16" s="58">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="111" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S16" s="59" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T16" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U16" s="59" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V16" s="60" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W16" s="55" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X16" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y16" s="62" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z16" s="63" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA16" s="64"/>
-      <c r="AB16" s="64"/>
-      <c r="AC16" s="64"/>
-      <c r="AD16" s="112"/>
-    </row>
-    <row r="17" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A17" s="43"/>
-      <c r="B17" s="44">
-        <v>8</v>
-      </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="50"/>
-      <c r="I17" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L17" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="54"/>
-      <c r="N17" s="55" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O17" s="56">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P17" s="57"/>
-      <c r="Q17" s="58">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="111" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S17" s="59" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T17" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U17" s="59" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V17" s="60" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W17" s="55" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X17" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y17" s="62" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z17" s="63" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA17" s="64"/>
-      <c r="AB17" s="64"/>
-      <c r="AC17" s="64"/>
-      <c r="AD17" s="112"/>
-    </row>
-    <row r="18" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A18" s="43"/>
-      <c r="B18" s="44">
-        <v>9</v>
-      </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G18" s="49"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L18" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="54"/>
-      <c r="N18" s="55" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O18" s="56">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P18" s="57"/>
-      <c r="Q18" s="58">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R18" s="111" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S18" s="59" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T18" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U18" s="59" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V18" s="60" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W18" s="55" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X18" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y18" s="62" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z18" s="63" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA18" s="64"/>
-      <c r="AB18" s="64"/>
-      <c r="AC18" s="64"/>
-      <c r="AD18" s="112"/>
-    </row>
-    <row r="19" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A19" s="43"/>
-      <c r="B19" s="44">
-        <v>10</v>
-      </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" s="49"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L19" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="54"/>
-      <c r="N19" s="55" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O19" s="56">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="58">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R19" s="111" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S19" s="59" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T19" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U19" s="59" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V19" s="60" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W19" s="55" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X19" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y19" s="62" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z19" s="63" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA19" s="64"/>
-      <c r="AB19" s="64"/>
-      <c r="AC19" s="64"/>
-      <c r="AD19" s="112"/>
-    </row>
-    <row r="20" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A20" s="43"/>
-      <c r="B20" s="44">
-        <v>11</v>
-      </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" s="49"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L20" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="54"/>
-      <c r="N20" s="55" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O20" s="56">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="57"/>
-      <c r="Q20" s="58">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R20" s="111" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S20" s="59" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T20" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U20" s="59" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V20" s="60" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W20" s="55" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X20" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y20" s="62" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z20" s="63" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA20" s="64"/>
-      <c r="AB20" s="64"/>
-      <c r="AC20" s="64"/>
-      <c r="AD20" s="112"/>
-    </row>
-    <row r="21" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A21" s="43"/>
-      <c r="B21" s="44">
-        <v>12</v>
-      </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G21" s="49"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L21" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="54"/>
-      <c r="N21" s="55" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O21" s="56">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P21" s="57"/>
-      <c r="Q21" s="58">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R21" s="111" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S21" s="59" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T21" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U21" s="59" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V21" s="60" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W21" s="55" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X21" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y21" s="62" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z21" s="63" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA21" s="64"/>
-      <c r="AB21" s="64"/>
-      <c r="AC21" s="64"/>
-      <c r="AD21" s="112"/>
-    </row>
-    <row r="22" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A22" s="43"/>
-      <c r="B22" s="44">
-        <v>13</v>
-      </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G22" s="49"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L22" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="54"/>
-      <c r="N22" s="55" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O22" s="56">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P22" s="57"/>
-      <c r="Q22" s="58">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R22" s="111" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S22" s="59" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T22" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U22" s="59" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V22" s="60" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W22" s="55" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X22" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y22" s="62" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z22" s="63" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA22" s="64"/>
-      <c r="AB22" s="64"/>
-      <c r="AC22" s="64"/>
-      <c r="AD22" s="112"/>
-    </row>
-    <row r="23" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A23" s="43"/>
-      <c r="B23" s="44">
-        <v>14</v>
-      </c>
-      <c r="C23" s="45"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G23" s="49"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L23" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="54"/>
-      <c r="N23" s="55" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O23" s="56">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P23" s="57"/>
-      <c r="Q23" s="58">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R23" s="111" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S23" s="59" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T23" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U23" s="59" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V23" s="60" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W23" s="55" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X23" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y23" s="62" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z23" s="63" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA23" s="64"/>
-      <c r="AB23" s="64"/>
-      <c r="AC23" s="64"/>
-      <c r="AD23" s="112"/>
-    </row>
-    <row r="24" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A24" s="43"/>
-      <c r="B24" s="44">
-        <v>15</v>
-      </c>
-      <c r="C24" s="45"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G24" s="49"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L24" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M24" s="54"/>
-      <c r="N24" s="55" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O24" s="56">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P24" s="57"/>
-      <c r="Q24" s="58">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R24" s="111" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S24" s="59" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T24" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U24" s="59" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V24" s="60" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W24" s="55" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X24" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y24" s="62" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z24" s="63" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA24" s="64"/>
-      <c r="AB24" s="64"/>
-      <c r="AC24" s="64"/>
-      <c r="AD24" s="112"/>
-    </row>
-    <row r="25" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A25" s="43"/>
-      <c r="B25" s="44">
-        <v>16</v>
-      </c>
-      <c r="C25" s="45"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G25" s="49"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L25" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M25" s="54"/>
-      <c r="N25" s="55" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O25" s="56">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P25" s="57"/>
-      <c r="Q25" s="58">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R25" s="111" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S25" s="59" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T25" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U25" s="59" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V25" s="60" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W25" s="55" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X25" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y25" s="62" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z25" s="63" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA25" s="64"/>
-      <c r="AB25" s="64"/>
-      <c r="AC25" s="64"/>
-      <c r="AD25" s="112"/>
-    </row>
-    <row r="26" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A26" s="43"/>
-      <c r="B26" s="44">
-        <v>17</v>
-      </c>
-      <c r="C26" s="45"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G26" s="49"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L26" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="54"/>
-      <c r="N26" s="55" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O26" s="56">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P26" s="57"/>
-      <c r="Q26" s="58">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R26" s="111" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S26" s="59" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T26" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U26" s="59" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V26" s="60" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W26" s="55" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X26" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y26" s="62" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z26" s="63" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA26" s="64"/>
-      <c r="AB26" s="64"/>
-      <c r="AC26" s="64"/>
-      <c r="AD26" s="112"/>
-    </row>
-    <row r="27" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A27" s="43"/>
-      <c r="B27" s="44">
-        <v>18</v>
-      </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G27" s="49"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J27" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L27" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M27" s="54"/>
-      <c r="N27" s="55" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O27" s="56">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P27" s="57"/>
-      <c r="Q27" s="58">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R27" s="111" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S27" s="59" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T27" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U27" s="59" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V27" s="60" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W27" s="55" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X27" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y27" s="62" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z27" s="63" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA27" s="64"/>
-      <c r="AB27" s="64"/>
-      <c r="AC27" s="64"/>
-      <c r="AD27" s="112"/>
-    </row>
-    <row r="28" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A28" s="43"/>
-      <c r="B28" s="44">
-        <v>19</v>
-      </c>
-      <c r="C28" s="45"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G28" s="49"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K28" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L28" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M28" s="54"/>
-      <c r="N28" s="55" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O28" s="56">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P28" s="57"/>
-      <c r="Q28" s="58">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R28" s="111" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S28" s="59" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T28" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U28" s="59" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V28" s="60" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W28" s="55" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X28" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y28" s="62" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z28" s="63" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA28" s="64"/>
-      <c r="AB28" s="64"/>
-      <c r="AC28" s="64"/>
-      <c r="AD28" s="112"/>
-    </row>
-    <row r="29" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A29" s="43"/>
-      <c r="B29" s="44">
-        <v>20</v>
-      </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G29" s="49"/>
-      <c r="H29" s="50"/>
-      <c r="I29" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L29" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M29" s="54"/>
-      <c r="N29" s="55" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O29" s="56">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P29" s="57"/>
-      <c r="Q29" s="58">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R29" s="111" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S29" s="59" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T29" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U29" s="59" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V29" s="60" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W29" s="55" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X29" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y29" s="62" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z29" s="63" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA29" s="64"/>
-      <c r="AB29" s="64"/>
-      <c r="AC29" s="64"/>
-      <c r="AD29" s="112"/>
-    </row>
-    <row r="30" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A30" s="43"/>
-      <c r="B30" s="44">
-        <v>21</v>
-      </c>
-      <c r="C30" s="45"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G30" s="49"/>
-      <c r="H30" s="50"/>
-      <c r="I30" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K30" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="L30" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M30" s="54"/>
-      <c r="N30" s="55" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O30" s="56">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P30" s="57"/>
-      <c r="Q30" s="58">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R30" s="111" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S30" s="59" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T30" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U30" s="59" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V30" s="60" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W30" s="55" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X30" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y30" s="62" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z30" s="63" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA30" s="64"/>
-      <c r="AB30" s="64"/>
-      <c r="AC30" s="64"/>
-      <c r="AD30" s="112"/>
-    </row>
-    <row r="31" spans="1:30" s="66" customFormat="1" ht="15" customHeight="1">
-      <c r="A31" s="43"/>
-      <c r="B31" s="67"/>
-      <c r="C31" s="68"/>
-      <c r="D31" s="68"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="70"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="50">
-        <f>SUM(I10:I30)</f>
-        <v>0</v>
-      </c>
-      <c r="J31" s="72"/>
-      <c r="K31" s="73"/>
-      <c r="L31" s="74"/>
-      <c r="M31" s="75"/>
-      <c r="N31" s="76"/>
-      <c r="O31" s="50">
-        <f>SUM(O10:O30)</f>
-        <v>0</v>
-      </c>
-      <c r="P31" s="77"/>
-      <c r="Q31" s="78">
-        <f>SUM(Q10:Q30)</f>
-        <v>0</v>
-      </c>
-      <c r="R31" s="79"/>
-      <c r="S31" s="50" t="e">
-        <f>SUM(S10:S30)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T31" s="80"/>
-      <c r="U31" s="80" t="e">
-        <f>SUM(U10:U30)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V31" s="81"/>
-      <c r="W31" s="82"/>
-      <c r="X31" s="83" t="e">
-        <f>AVERAGE(X10:X30)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y31" s="50" t="e">
-        <f>SUM(Y10:Y30)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z31" s="84" t="e">
-        <f>(I31-O31-S31-U31-Y31-AA31-AC31-AB31)/I31</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA31" s="64"/>
-      <c r="AB31" s="64"/>
-      <c r="AC31" s="64"/>
-      <c r="AD31" s="8"/>
-    </row>
-    <row r="32" spans="1:30" s="66" customFormat="1" ht="15" customHeight="1">
-      <c r="A32" s="43"/>
-      <c r="B32" s="67"/>
-      <c r="C32" s="85"/>
-      <c r="D32" s="86"/>
-      <c r="E32" s="85"/>
-      <c r="F32" s="87"/>
-      <c r="G32" s="88"/>
-      <c r="H32" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="I32" s="50">
-        <f>I31*1.2</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="89"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="90"/>
-      <c r="M32" s="91"/>
-      <c r="N32" s="91"/>
-      <c r="O32" s="92"/>
-      <c r="P32" s="93"/>
-      <c r="Q32" s="94"/>
-      <c r="R32" s="95"/>
-      <c r="S32" s="96"/>
-      <c r="T32" s="97"/>
-      <c r="U32" s="98"/>
-      <c r="V32" s="81"/>
-      <c r="W32" s="82"/>
-      <c r="X32" s="99"/>
-      <c r="Y32" s="100"/>
-      <c r="Z32" s="101"/>
-      <c r="AC32" s="102"/>
-      <c r="AD32" s="65"/>
-    </row>
-    <row r="33" spans="1:30" s="1" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A33" s="103" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" s="137" t="s">
-        <v>45</v>
-      </c>
-      <c r="C33" s="138"/>
-      <c r="D33" s="113"/>
-      <c r="E33" s="113"/>
-      <c r="F33" s="136"/>
-      <c r="G33" s="136"/>
-      <c r="H33" s="136"/>
-      <c r="K33" s="104"/>
-      <c r="L33" s="104"/>
+      <c r="J33"/>
+      <c r="K33"/>
+      <c r="L33"/>
+      <c r="M33"/>
+      <c r="N33"/>
+      <c r="O33"/>
       <c r="P33"/>
       <c r="Q33"/>
       <c r="R33"/>
@@ -7686,28 +6807,33 @@
       <c r="Y33"/>
       <c r="Z33"/>
       <c r="AA33"/>
-      <c r="AD33" s="15"/>
+      <c r="AB33" s="103"/>
+      <c r="AC33" s="103"/>
+      <c r="AD33" s="103"/>
+      <c r="AE33" s="103"/>
+      <c r="AF33" s="103"/>
     </row>
-    <row r="34" spans="1:30" ht="14.1" customHeight="1">
-      <c r="A34" s="103" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" s="114" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="115"/>
-      <c r="D34" s="115"/>
-      <c r="E34" s="115"/>
-      <c r="F34" s="115"/>
-      <c r="G34" s="115"/>
-      <c r="H34" s="115"/>
-      <c r="I34" s="116"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="104"/>
-      <c r="L34" s="104"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="121"/>
+    <row r="34" spans="1:33" s="100" customFormat="1" ht="15" customHeight="1">
+      <c r="A34" s="106"/>
+      <c r="B34" s="135" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="125"/>
+      <c r="D34" s="125"/>
+      <c r="E34" s="125"/>
+      <c r="F34" s="125"/>
+      <c r="G34" s="125"/>
+      <c r="H34" s="126"/>
+      <c r="I34" s="128">
+        <f>AA11</f>
+        <v>0</v>
+      </c>
+      <c r="J34"/>
+      <c r="K34"/>
+      <c r="L34"/>
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
       <c r="P34"/>
       <c r="Q34"/>
       <c r="R34"/>
@@ -7720,31 +6846,34 @@
       <c r="Y34"/>
       <c r="Z34"/>
       <c r="AA34"/>
+      <c r="AB34" s="103"/>
+      <c r="AC34" s="103"/>
+      <c r="AD34" s="103"/>
+      <c r="AE34" s="103"/>
+      <c r="AF34" s="103"/>
+      <c r="AG34" s="103"/>
     </row>
-    <row r="35" spans="1:30" s="1" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A35" s="103" t="s">
-        <v>20</v>
-      </c>
-      <c r="B35" s="114" t="s">
-        <v>47</v>
-      </c>
-      <c r="C35" s="115"/>
-      <c r="D35" s="115"/>
-      <c r="E35" s="115"/>
-      <c r="F35" s="115"/>
-      <c r="G35" s="115"/>
-      <c r="H35" s="115"/>
-      <c r="I35" s="119">
-        <v>150</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K35" s="104">
-        <f>I35+I36</f>
-        <v>180</v>
-      </c>
-      <c r="L35" s="104"/>
+    <row r="35" spans="1:33" s="100" customFormat="1" ht="15" customHeight="1">
+      <c r="A35" s="106"/>
+      <c r="B35" s="135" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="125"/>
+      <c r="D35" s="125"/>
+      <c r="E35" s="125"/>
+      <c r="F35" s="125"/>
+      <c r="G35" s="125"/>
+      <c r="H35" s="126"/>
+      <c r="I35" s="128">
+        <f>AB11</f>
+        <v>0</v>
+      </c>
+      <c r="J35"/>
+      <c r="K35"/>
+      <c r="L35"/>
+      <c r="M35"/>
+      <c r="N35"/>
+      <c r="O35"/>
       <c r="P35"/>
       <c r="Q35"/>
       <c r="R35"/>
@@ -7757,33 +6886,34 @@
       <c r="Y35"/>
       <c r="Z35"/>
       <c r="AA35"/>
+      <c r="AB35" s="103"/>
+      <c r="AC35" s="103"/>
+      <c r="AD35" s="103"/>
+      <c r="AE35" s="103"/>
+      <c r="AF35" s="103"/>
+      <c r="AG35" s="103"/>
     </row>
-    <row r="36" spans="1:30" s="42" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A36" s="103" t="s">
-        <v>14</v>
-      </c>
-      <c r="B36" s="117" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" s="118"/>
-      <c r="D36" s="118"/>
-      <c r="E36" s="118"/>
-      <c r="F36" s="118"/>
-      <c r="G36" s="118"/>
-      <c r="H36" s="118"/>
-      <c r="I36" s="120">
-        <v>30</v>
-      </c>
-      <c r="J36" s="122"/>
-      <c r="K36" s="104"/>
-      <c r="L36" s="104"/>
-      <c r="N36" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O36" s="123">
-        <f>I31*14</f>
+    <row r="36" spans="1:33" s="100" customFormat="1" ht="15" customHeight="1">
+      <c r="A36" s="106"/>
+      <c r="B36" s="135" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="125"/>
+      <c r="D36" s="125"/>
+      <c r="E36" s="125"/>
+      <c r="F36" s="125"/>
+      <c r="G36" s="125"/>
+      <c r="H36" s="126"/>
+      <c r="I36" s="128">
+        <f>AC11</f>
         <v>0</v>
       </c>
+      <c r="J36"/>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
       <c r="P36"/>
       <c r="Q36"/>
       <c r="R36"/>
@@ -7796,31 +6926,36 @@
       <c r="Y36"/>
       <c r="Z36"/>
       <c r="AA36"/>
+      <c r="AB36" s="103"/>
+      <c r="AC36" s="103"/>
+      <c r="AD36" s="103"/>
+      <c r="AE36" s="103"/>
+      <c r="AF36" s="103"/>
+      <c r="AG36" s="103"/>
     </row>
-    <row r="37" spans="1:30" ht="14.1" customHeight="1">
-      <c r="A37" s="103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" s="130" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37" s="131"/>
-      <c r="D37" s="131"/>
-      <c r="E37" s="131"/>
-      <c r="F37" s="131"/>
-      <c r="G37" s="131"/>
-      <c r="H37" s="132"/>
-      <c r="I37" s="124"/>
-      <c r="J37" s="125"/>
-      <c r="K37" s="104"/>
-      <c r="L37" s="104"/>
-      <c r="N37" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="O37" s="123">
-        <f>I32*14</f>
+    <row r="37" spans="1:33" s="100" customFormat="1" ht="15" customHeight="1">
+      <c r="A37" s="106"/>
+      <c r="B37" s="136" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="137"/>
+      <c r="D37" s="137"/>
+      <c r="E37" s="137"/>
+      <c r="F37" s="137"/>
+      <c r="G37" s="134"/>
+      <c r="H37" s="132" t="s">
+        <v>67</v>
+      </c>
+      <c r="I37" s="133">
+        <f>IF(H37="ДА",I24*3%/365*(I15+I16),0)</f>
         <v>0</v>
       </c>
+      <c r="J37"/>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
       <c r="P37"/>
       <c r="Q37"/>
       <c r="R37"/>
@@ -7833,24 +6968,34 @@
       <c r="Y37"/>
       <c r="Z37"/>
       <c r="AA37"/>
+      <c r="AB37" s="103"/>
+      <c r="AC37" s="103"/>
+      <c r="AD37" s="103"/>
+      <c r="AE37" s="103"/>
+      <c r="AF37" s="103"/>
+      <c r="AG37" s="103"/>
     </row>
-    <row r="38" spans="1:30" ht="14.1" customHeight="1">
-      <c r="A38" s="103" t="s">
-        <v>16</v>
-      </c>
-      <c r="B38" s="130" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" s="131"/>
-      <c r="D38" s="131"/>
-      <c r="E38" s="131"/>
-      <c r="F38" s="131"/>
-      <c r="G38" s="131"/>
-      <c r="H38" s="132"/>
-      <c r="I38" s="126"/>
-      <c r="J38" s="127"/>
-      <c r="K38" s="104"/>
-      <c r="L38" s="104"/>
+    <row r="38" spans="1:33" s="100" customFormat="1" ht="15" customHeight="1">
+      <c r="A38" s="106"/>
+      <c r="B38" s="135" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="125"/>
+      <c r="D38" s="125"/>
+      <c r="E38" s="125"/>
+      <c r="F38" s="125"/>
+      <c r="G38" s="125"/>
+      <c r="H38" s="126"/>
+      <c r="I38" s="128">
+        <f>I26-I27</f>
+        <v>0</v>
+      </c>
+      <c r="J38"/>
+      <c r="K38"/>
+      <c r="L38"/>
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38"/>
       <c r="P38"/>
       <c r="Q38"/>
       <c r="R38"/>
@@ -7863,28 +7008,31 @@
       <c r="Y38"/>
       <c r="Z38"/>
       <c r="AA38"/>
+      <c r="AB38" s="103"/>
+      <c r="AC38" s="103"/>
+      <c r="AD38" s="103"/>
+      <c r="AE38" s="103"/>
+      <c r="AF38" s="103"/>
+      <c r="AG38" s="103"/>
     </row>
-    <row r="39" spans="1:30" ht="14.1" customHeight="1">
-      <c r="A39" s="103" t="s">
-        <v>17</v>
-      </c>
-      <c r="B39" s="130" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39" s="131"/>
-      <c r="D39" s="131"/>
-      <c r="E39" s="131"/>
-      <c r="F39" s="131"/>
-      <c r="G39" s="131"/>
-      <c r="H39" s="132"/>
-      <c r="I39" s="128">
-        <f>I31</f>
-        <v>0</v>
-      </c>
-      <c r="J39" s="129"/>
-      <c r="K39" s="104"/>
-      <c r="L39" s="104"/>
-      <c r="M39" s="8"/>
+    <row r="39" spans="1:33" s="100" customFormat="1" ht="15" customHeight="1">
+      <c r="A39" s="106"/>
+      <c r="B39" s="135" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="125"/>
+      <c r="D39" s="125"/>
+      <c r="E39" s="125"/>
+      <c r="F39" s="125"/>
+      <c r="G39" s="125"/>
+      <c r="H39" s="126"/>
+      <c r="I39" s="128"/>
+      <c r="J39"/>
+      <c r="K39"/>
+      <c r="L39"/>
+      <c r="M39"/>
+      <c r="N39"/>
+      <c r="O39"/>
       <c r="P39"/>
       <c r="Q39"/>
       <c r="R39"/>
@@ -7897,19 +7045,28 @@
       <c r="Y39"/>
       <c r="Z39"/>
       <c r="AA39"/>
+      <c r="AB39" s="103"/>
+      <c r="AC39" s="103"/>
+      <c r="AD39" s="103"/>
+      <c r="AE39" s="103"/>
+      <c r="AF39" s="103"/>
+      <c r="AG39" s="103"/>
     </row>
-    <row r="40" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1">
-      <c r="A40" s="103" t="s">
-        <v>18</v>
-      </c>
-      <c r="B40" s="130"/>
-      <c r="C40" s="131"/>
-      <c r="D40" s="131"/>
-      <c r="E40" s="131"/>
-      <c r="F40" s="131"/>
-      <c r="G40" s="131"/>
-      <c r="H40" s="132"/>
-      <c r="I40" s="128"/>
+    <row r="40" spans="1:33" s="100" customFormat="1" ht="15" customHeight="1">
+      <c r="A40" s="106"/>
+      <c r="B40" s="135" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="125"/>
+      <c r="D40" s="125"/>
+      <c r="E40" s="125"/>
+      <c r="F40" s="125"/>
+      <c r="G40" s="125"/>
+      <c r="H40" s="126"/>
+      <c r="I40" s="162" t="e">
+        <f>I38/I26</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="J40"/>
       <c r="K40"/>
       <c r="L40"/>
@@ -7928,19 +7085,23 @@
       <c r="Y40"/>
       <c r="Z40"/>
       <c r="AA40"/>
+      <c r="AB40" s="103"/>
+      <c r="AC40" s="103"/>
+      <c r="AD40" s="103"/>
+      <c r="AE40" s="103"/>
+      <c r="AF40" s="103"/>
+      <c r="AG40" s="103"/>
     </row>
-    <row r="41" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1">
-      <c r="A41" s="103" t="s">
-        <v>19</v>
-      </c>
-      <c r="B41" s="130"/>
-      <c r="C41" s="131"/>
-      <c r="D41" s="131"/>
-      <c r="E41" s="131"/>
-      <c r="F41" s="131"/>
-      <c r="G41" s="131"/>
-      <c r="H41" s="132"/>
-      <c r="I41" s="128"/>
+    <row r="41" spans="1:33" s="100" customFormat="1" ht="12" customHeight="1">
+      <c r="A41" s="1"/>
+      <c r="B41"/>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
+      <c r="I41"/>
       <c r="J41"/>
       <c r="K41"/>
       <c r="L41"/>
@@ -7959,19 +7120,22 @@
       <c r="Y41"/>
       <c r="Z41"/>
       <c r="AA41"/>
+      <c r="AB41" s="8"/>
+      <c r="AC41" s="8"/>
+      <c r="AD41" s="8"/>
+      <c r="AE41" s="8"/>
+      <c r="AF41" s="8"/>
+      <c r="AG41" s="8"/>
     </row>
-    <row r="42" spans="1:30" s="1" customFormat="1" ht="11.1" customHeight="1">
-      <c r="A42" s="103" t="s">
-        <v>16</v>
-      </c>
-      <c r="B42" s="130"/>
-      <c r="C42" s="131"/>
-      <c r="D42" s="131"/>
-      <c r="E42" s="131"/>
-      <c r="F42" s="131"/>
-      <c r="G42" s="131"/>
-      <c r="H42" s="132"/>
-      <c r="I42" s="128"/>
+    <row r="42" spans="1:33" s="1" customFormat="1" ht="11.25" customHeight="1">
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
       <c r="J42"/>
       <c r="K42"/>
       <c r="L42"/>
@@ -7990,19 +7154,25 @@
       <c r="Y42"/>
       <c r="Z42"/>
       <c r="AA42"/>
+      <c r="AB42" s="8"/>
+      <c r="AC42" s="8"/>
+      <c r="AD42" s="8"/>
+      <c r="AE42" s="8"/>
+      <c r="AF42" s="8"/>
+      <c r="AG42" s="8"/>
     </row>
-    <row r="43" spans="1:30" s="108" customFormat="1" ht="15" customHeight="1">
-      <c r="A43" s="105" t="s">
-        <v>17</v>
-      </c>
-      <c r="B43" s="130"/>
-      <c r="C43" s="131"/>
-      <c r="D43" s="131"/>
-      <c r="E43" s="131"/>
-      <c r="F43" s="131"/>
-      <c r="G43" s="131"/>
-      <c r="H43" s="132"/>
-      <c r="I43" s="128"/>
+    <row r="43" spans="1:33" s="1" customFormat="1" ht="11.45" customHeight="1">
+      <c r="C43" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43"/>
+      <c r="I43"/>
       <c r="J43"/>
       <c r="K43"/>
       <c r="L43"/>
@@ -8021,20 +7191,25 @@
       <c r="Y43"/>
       <c r="Z43"/>
       <c r="AA43"/>
+      <c r="AB43" s="8"/>
+      <c r="AC43" s="8"/>
+      <c r="AD43" s="8"/>
+      <c r="AE43" s="8"/>
+      <c r="AF43" s="8"/>
+      <c r="AG43" s="8"/>
     </row>
-    <row r="44" spans="1:30" s="106" customFormat="1" ht="15" customHeight="1">
-      <c r="A44" s="109"/>
-      <c r="B44" s="130"/>
-      <c r="C44" s="131"/>
-      <c r="D44" s="131"/>
-      <c r="E44" s="131"/>
-      <c r="F44" s="131"/>
-      <c r="G44" s="131"/>
-      <c r="H44" s="132"/>
-      <c r="I44" s="133">
-        <f>$I$32</f>
-        <v>0</v>
-      </c>
+    <row r="44" spans="1:33" ht="11.45" customHeight="1">
+      <c r="C44" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44"/>
+      <c r="I44"/>
       <c r="J44"/>
       <c r="K44"/>
       <c r="L44"/>
@@ -8054,8 +7229,7 @@
       <c r="Z44"/>
       <c r="AA44"/>
     </row>
-    <row r="45" spans="1:30" s="66" customFormat="1" ht="15" customHeight="1">
-      <c r="A45" s="43"/>
+    <row r="45" spans="1:33" ht="11.45" customHeight="1">
       <c r="B45"/>
       <c r="C45"/>
       <c r="D45"/>
@@ -8083,8 +7257,7 @@
       <c r="Z45"/>
       <c r="AA45"/>
     </row>
-    <row r="46" spans="1:30" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A46" s="110"/>
+    <row r="46" spans="1:33" ht="11.45" customHeight="1">
       <c r="B46"/>
       <c r="C46"/>
       <c r="D46"/>
@@ -8112,8 +7285,7 @@
       <c r="Z46"/>
       <c r="AA46"/>
     </row>
-    <row r="47" spans="1:30" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A47" s="110"/>
+    <row r="47" spans="1:33" ht="11.45" customHeight="1">
       <c r="B47"/>
       <c r="C47"/>
       <c r="D47"/>
@@ -8141,687 +7313,27 @@
       <c r="Z47"/>
       <c r="AA47"/>
     </row>
-    <row r="48" spans="1:30" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A48" s="110"/>
-      <c r="B48" s="134" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" s="154" t="s">
-        <v>56</v>
-      </c>
-      <c r="D48" s="155"/>
-      <c r="E48" s="155"/>
-      <c r="F48" s="155"/>
-      <c r="G48" s="155"/>
-      <c r="H48" s="155"/>
-      <c r="I48" s="156"/>
-      <c r="J48"/>
-      <c r="K48"/>
-      <c r="L48"/>
-      <c r="M48"/>
-      <c r="N48"/>
-      <c r="O48"/>
-      <c r="P48"/>
-      <c r="Q48"/>
-      <c r="R48"/>
-      <c r="S48"/>
-      <c r="T48"/>
-      <c r="U48"/>
-      <c r="V48"/>
-      <c r="W48"/>
-      <c r="X48"/>
-      <c r="Y48"/>
-      <c r="Z48"/>
-      <c r="AA48"/>
-    </row>
-    <row r="49" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A49" s="110"/>
-      <c r="B49" s="135">
-        <v>1</v>
-      </c>
-      <c r="C49" s="151" t="s">
-        <v>57</v>
-      </c>
-      <c r="D49" s="152"/>
-      <c r="E49" s="152"/>
-      <c r="F49" s="152"/>
-      <c r="G49" s="152"/>
-      <c r="H49" s="153"/>
-      <c r="I49" s="133">
-        <f>I37</f>
-        <v>0</v>
-      </c>
-      <c r="J49"/>
-      <c r="K49"/>
-      <c r="L49"/>
-      <c r="M49"/>
-      <c r="N49"/>
-      <c r="O49"/>
-      <c r="P49"/>
-      <c r="Q49"/>
-      <c r="R49"/>
-      <c r="S49"/>
-      <c r="T49"/>
-      <c r="U49"/>
-      <c r="V49"/>
-      <c r="W49"/>
-      <c r="X49"/>
-      <c r="Y49"/>
-      <c r="Z49"/>
-      <c r="AA49"/>
-    </row>
-    <row r="50" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A50" s="110"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="151" t="s">
-        <v>58</v>
-      </c>
-      <c r="D50" s="152"/>
-      <c r="E50" s="152"/>
-      <c r="F50" s="152"/>
-      <c r="G50" s="152"/>
-      <c r="H50" s="153"/>
-      <c r="I50" s="150">
-        <f>I49/120*20</f>
-        <v>0</v>
-      </c>
-      <c r="J50"/>
-      <c r="K50"/>
-      <c r="L50"/>
-      <c r="M50"/>
-      <c r="N50"/>
-      <c r="O50"/>
-      <c r="P50"/>
-      <c r="Q50"/>
-      <c r="R50"/>
-      <c r="S50"/>
-      <c r="T50"/>
-      <c r="U50"/>
-      <c r="V50"/>
-      <c r="W50"/>
-      <c r="X50"/>
-      <c r="Y50"/>
-      <c r="Z50"/>
-      <c r="AA50"/>
-    </row>
-    <row r="51" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A51" s="110"/>
-      <c r="B51"/>
-      <c r="C51"/>
-      <c r="D51"/>
-      <c r="E51"/>
-      <c r="F51"/>
-      <c r="G51"/>
-      <c r="H51"/>
-      <c r="I51"/>
-      <c r="J51"/>
-      <c r="K51"/>
-      <c r="L51"/>
-      <c r="M51"/>
-      <c r="N51"/>
-      <c r="O51"/>
-      <c r="P51"/>
-      <c r="Q51"/>
-      <c r="R51"/>
-      <c r="S51"/>
-      <c r="T51"/>
-      <c r="U51"/>
-      <c r="V51"/>
-      <c r="W51"/>
-      <c r="X51"/>
-      <c r="Y51"/>
-      <c r="Z51"/>
-      <c r="AA51"/>
-      <c r="AB51" s="107"/>
-      <c r="AC51" s="107"/>
-      <c r="AD51" s="107"/>
-      <c r="AE51" s="107"/>
-      <c r="AF51" s="107"/>
-    </row>
-    <row r="52" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A52" s="110"/>
-      <c r="B52"/>
-      <c r="C52"/>
-      <c r="D52"/>
-      <c r="E52"/>
-      <c r="F52"/>
-      <c r="G52"/>
-      <c r="H52"/>
-      <c r="I52"/>
-      <c r="J52"/>
-      <c r="K52"/>
-      <c r="L52"/>
-      <c r="M52"/>
-      <c r="N52"/>
-      <c r="O52"/>
-      <c r="P52"/>
-      <c r="Q52"/>
-      <c r="R52"/>
-      <c r="S52"/>
-      <c r="T52"/>
-      <c r="U52"/>
-      <c r="V52"/>
-      <c r="W52"/>
-      <c r="X52"/>
-      <c r="Y52"/>
-      <c r="Z52"/>
-      <c r="AA52"/>
-      <c r="AB52" s="107"/>
-      <c r="AC52" s="107"/>
-      <c r="AD52" s="107"/>
-      <c r="AE52" s="107"/>
-      <c r="AF52" s="107"/>
-    </row>
-    <row r="53" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A53" s="110"/>
-      <c r="B53"/>
-      <c r="C53"/>
-      <c r="D53"/>
-      <c r="E53"/>
-      <c r="F53"/>
-      <c r="G53"/>
-      <c r="H53"/>
-      <c r="I53"/>
-      <c r="J53"/>
-      <c r="K53"/>
-      <c r="L53"/>
-      <c r="M53"/>
-      <c r="N53"/>
-      <c r="O53"/>
-      <c r="P53"/>
-      <c r="Q53"/>
-      <c r="R53"/>
-      <c r="S53"/>
-      <c r="T53"/>
-      <c r="U53"/>
-      <c r="V53"/>
-      <c r="W53"/>
-      <c r="X53"/>
-      <c r="Y53"/>
-      <c r="Z53"/>
-      <c r="AA53"/>
-      <c r="AB53" s="107"/>
-      <c r="AC53" s="107"/>
-      <c r="AD53" s="107"/>
-      <c r="AE53" s="107"/>
-      <c r="AF53" s="107"/>
-    </row>
-    <row r="54" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A54" s="110"/>
-      <c r="B54"/>
-      <c r="C54"/>
-      <c r="D54"/>
-      <c r="E54"/>
-      <c r="F54"/>
-      <c r="G54"/>
-      <c r="H54"/>
-      <c r="I54"/>
-      <c r="J54"/>
-      <c r="K54"/>
-      <c r="L54"/>
-      <c r="M54"/>
-      <c r="N54"/>
-      <c r="O54"/>
-      <c r="P54"/>
-      <c r="Q54"/>
-      <c r="R54"/>
-      <c r="S54"/>
-      <c r="T54"/>
-      <c r="U54"/>
-      <c r="V54"/>
-      <c r="W54"/>
-      <c r="X54"/>
-      <c r="Y54"/>
-      <c r="Z54"/>
-      <c r="AA54"/>
-      <c r="AB54" s="107"/>
-      <c r="AC54" s="107"/>
-      <c r="AD54" s="107"/>
-      <c r="AE54" s="107"/>
-      <c r="AF54" s="107"/>
-      <c r="AG54" s="107"/>
-    </row>
-    <row r="55" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A55" s="110"/>
-      <c r="B55"/>
-      <c r="C55"/>
-      <c r="D55"/>
-      <c r="E55"/>
-      <c r="F55"/>
-      <c r="G55"/>
-      <c r="H55"/>
-      <c r="I55"/>
-      <c r="J55"/>
-      <c r="K55"/>
-      <c r="L55"/>
-      <c r="M55"/>
-      <c r="N55"/>
-      <c r="O55"/>
-      <c r="P55"/>
-      <c r="Q55"/>
-      <c r="R55"/>
-      <c r="S55"/>
-      <c r="T55"/>
-      <c r="U55"/>
-      <c r="V55"/>
-      <c r="W55"/>
-      <c r="X55"/>
-      <c r="Y55"/>
-      <c r="Z55"/>
-      <c r="AA55"/>
-      <c r="AB55" s="107"/>
-      <c r="AC55" s="107"/>
-      <c r="AD55" s="107"/>
-      <c r="AE55" s="107"/>
-      <c r="AF55" s="107"/>
-      <c r="AG55" s="107"/>
-    </row>
-    <row r="56" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A56" s="110"/>
-      <c r="B56"/>
-      <c r="C56"/>
-      <c r="D56"/>
-      <c r="E56"/>
-      <c r="F56"/>
-      <c r="G56"/>
-      <c r="H56"/>
-      <c r="I56"/>
-      <c r="J56"/>
-      <c r="K56"/>
-      <c r="L56"/>
-      <c r="M56"/>
-      <c r="N56"/>
-      <c r="O56"/>
-      <c r="P56"/>
-      <c r="Q56"/>
-      <c r="R56"/>
-      <c r="S56"/>
-      <c r="T56"/>
-      <c r="U56"/>
-      <c r="V56"/>
-      <c r="W56"/>
-      <c r="X56"/>
-      <c r="Y56"/>
-      <c r="Z56"/>
-      <c r="AA56"/>
-      <c r="AB56" s="107"/>
-      <c r="AC56" s="107"/>
-      <c r="AD56" s="107"/>
-      <c r="AE56" s="107"/>
-      <c r="AF56" s="107"/>
-      <c r="AG56" s="107"/>
-    </row>
-    <row r="57" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A57" s="110"/>
-      <c r="B57"/>
-      <c r="C57"/>
-      <c r="D57"/>
-      <c r="E57"/>
-      <c r="F57"/>
-      <c r="G57"/>
-      <c r="H57"/>
-      <c r="I57"/>
-      <c r="J57"/>
-      <c r="K57"/>
-      <c r="L57"/>
-      <c r="M57"/>
-      <c r="N57"/>
-      <c r="O57"/>
-      <c r="P57"/>
-      <c r="Q57"/>
-      <c r="R57"/>
-      <c r="S57"/>
-      <c r="T57"/>
-      <c r="U57"/>
-      <c r="V57"/>
-      <c r="W57"/>
-      <c r="X57"/>
-      <c r="Y57"/>
-      <c r="Z57"/>
-      <c r="AA57"/>
-      <c r="AB57" s="107"/>
-      <c r="AC57" s="107"/>
-      <c r="AD57" s="107"/>
-      <c r="AE57" s="107"/>
-      <c r="AF57" s="107"/>
-      <c r="AG57" s="107"/>
-    </row>
-    <row r="58" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A58" s="110"/>
-      <c r="B58"/>
-      <c r="C58"/>
-      <c r="D58"/>
-      <c r="E58"/>
-      <c r="F58"/>
-      <c r="G58"/>
-      <c r="H58"/>
-      <c r="I58"/>
-      <c r="J58"/>
-      <c r="K58"/>
-      <c r="L58"/>
-      <c r="M58"/>
-      <c r="N58"/>
-      <c r="O58"/>
-      <c r="P58"/>
-      <c r="Q58"/>
-      <c r="R58"/>
-      <c r="S58"/>
-      <c r="T58"/>
-      <c r="U58"/>
-      <c r="V58"/>
-      <c r="W58"/>
-      <c r="X58"/>
-      <c r="Y58"/>
-      <c r="Z58"/>
-      <c r="AA58"/>
-      <c r="AB58" s="107"/>
-      <c r="AC58" s="107"/>
-      <c r="AD58" s="107"/>
-      <c r="AE58" s="107"/>
-      <c r="AF58" s="107"/>
-      <c r="AG58" s="107"/>
-    </row>
-    <row r="59" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A59" s="110"/>
-      <c r="B59"/>
-      <c r="C59"/>
-      <c r="D59"/>
-      <c r="E59"/>
-      <c r="F59"/>
-      <c r="G59"/>
-      <c r="H59"/>
-      <c r="I59"/>
-      <c r="J59"/>
-      <c r="K59"/>
-      <c r="L59"/>
-      <c r="M59"/>
-      <c r="N59"/>
-      <c r="O59"/>
-      <c r="P59"/>
-      <c r="Q59"/>
-      <c r="R59"/>
-      <c r="S59"/>
-      <c r="T59"/>
-      <c r="U59"/>
-      <c r="V59"/>
-      <c r="W59"/>
-      <c r="X59"/>
-      <c r="Y59"/>
-      <c r="Z59"/>
-      <c r="AA59"/>
-      <c r="AB59" s="107"/>
-      <c r="AC59" s="107"/>
-      <c r="AD59" s="107"/>
-      <c r="AE59" s="107"/>
-      <c r="AF59" s="107"/>
-      <c r="AG59" s="107"/>
-    </row>
-    <row r="60" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A60" s="110"/>
-      <c r="B60"/>
-      <c r="C60"/>
-      <c r="D60"/>
-      <c r="E60"/>
-      <c r="F60"/>
-      <c r="G60"/>
-      <c r="H60"/>
-      <c r="I60"/>
-      <c r="J60"/>
-      <c r="K60"/>
-      <c r="L60"/>
-      <c r="M60"/>
-      <c r="N60"/>
-      <c r="O60"/>
-      <c r="P60"/>
-      <c r="Q60"/>
-      <c r="R60"/>
-      <c r="S60"/>
-      <c r="T60"/>
-      <c r="U60"/>
-      <c r="V60"/>
-      <c r="W60"/>
-      <c r="X60"/>
-      <c r="Y60"/>
-      <c r="Z60"/>
-      <c r="AA60"/>
-      <c r="AB60" s="107"/>
-      <c r="AC60" s="107"/>
-      <c r="AD60" s="107"/>
-      <c r="AE60" s="107"/>
-      <c r="AF60" s="107"/>
-      <c r="AG60" s="107"/>
-    </row>
-    <row r="61" spans="1:33" s="104" customFormat="1" ht="12" customHeight="1">
-      <c r="A61" s="1"/>
-      <c r="B61"/>
-      <c r="C61"/>
-      <c r="D61"/>
-      <c r="E61"/>
-      <c r="F61"/>
-      <c r="G61"/>
-      <c r="H61"/>
-      <c r="I61"/>
-      <c r="J61"/>
-      <c r="K61"/>
-      <c r="L61"/>
-      <c r="M61"/>
-      <c r="N61"/>
-      <c r="O61"/>
-      <c r="P61"/>
-      <c r="Q61"/>
-      <c r="R61"/>
-      <c r="S61"/>
-      <c r="T61"/>
-      <c r="U61"/>
-      <c r="V61"/>
-      <c r="W61"/>
-      <c r="X61"/>
-      <c r="Y61"/>
-      <c r="Z61"/>
-      <c r="AA61"/>
-      <c r="AB61" s="8"/>
-      <c r="AC61" s="8"/>
-      <c r="AD61" s="8"/>
-      <c r="AE61" s="8"/>
-      <c r="AF61" s="8"/>
-      <c r="AG61" s="8"/>
-    </row>
-    <row r="62" spans="1:33" s="1" customFormat="1" ht="11.25" customHeight="1">
-      <c r="B62"/>
-      <c r="C62"/>
-      <c r="D62"/>
-      <c r="E62"/>
-      <c r="F62"/>
-      <c r="G62"/>
-      <c r="H62"/>
-      <c r="I62"/>
-      <c r="J62"/>
-      <c r="K62"/>
-      <c r="L62"/>
-      <c r="M62"/>
-      <c r="N62"/>
-      <c r="O62"/>
-      <c r="P62"/>
-      <c r="Q62"/>
-      <c r="R62"/>
-      <c r="S62"/>
-      <c r="T62"/>
-      <c r="U62"/>
-      <c r="V62"/>
-      <c r="W62"/>
-      <c r="X62"/>
-      <c r="Y62"/>
-      <c r="Z62"/>
-      <c r="AA62"/>
-      <c r="AB62" s="8"/>
-      <c r="AC62" s="8"/>
-      <c r="AD62" s="8"/>
-      <c r="AE62" s="8"/>
-      <c r="AF62" s="8"/>
-      <c r="AG62" s="8"/>
-    </row>
-    <row r="63" spans="1:33" s="1" customFormat="1" ht="11.45" customHeight="1">
-      <c r="B63"/>
-      <c r="C63"/>
-      <c r="D63"/>
-      <c r="E63"/>
-      <c r="F63"/>
-      <c r="G63"/>
-      <c r="H63"/>
-      <c r="I63"/>
-      <c r="J63"/>
-      <c r="K63"/>
-      <c r="L63"/>
-      <c r="M63"/>
-      <c r="N63"/>
-      <c r="O63"/>
-      <c r="P63"/>
-      <c r="Q63"/>
-      <c r="R63"/>
-      <c r="S63"/>
-      <c r="T63"/>
-      <c r="U63"/>
-      <c r="V63"/>
-      <c r="W63"/>
-      <c r="X63"/>
-      <c r="Y63"/>
-      <c r="Z63"/>
-      <c r="AA63"/>
-      <c r="AB63" s="8"/>
-      <c r="AC63" s="8"/>
-      <c r="AD63" s="8"/>
-      <c r="AE63" s="8"/>
-      <c r="AF63" s="8"/>
-      <c r="AG63" s="8"/>
-    </row>
-    <row r="64" spans="1:33" ht="11.45" customHeight="1">
-      <c r="B64"/>
-      <c r="C64"/>
-      <c r="D64"/>
-      <c r="E64"/>
-      <c r="F64"/>
-      <c r="G64"/>
-      <c r="H64"/>
-      <c r="I64"/>
-      <c r="J64"/>
-      <c r="K64"/>
-      <c r="L64"/>
-      <c r="M64"/>
-      <c r="N64"/>
-      <c r="O64"/>
-      <c r="P64"/>
-      <c r="Q64"/>
-      <c r="R64"/>
-      <c r="S64"/>
-      <c r="T64"/>
-      <c r="U64"/>
-      <c r="V64"/>
-      <c r="W64"/>
-      <c r="X64"/>
-      <c r="Y64"/>
-      <c r="Z64"/>
-      <c r="AA64"/>
-    </row>
-    <row r="65" spans="2:27" ht="11.45" customHeight="1">
-      <c r="B65"/>
-      <c r="C65"/>
-      <c r="D65"/>
-      <c r="E65"/>
-      <c r="F65"/>
-      <c r="G65"/>
-      <c r="H65"/>
-      <c r="I65"/>
-      <c r="J65"/>
-      <c r="K65"/>
-      <c r="L65"/>
-      <c r="M65"/>
-      <c r="N65"/>
-      <c r="O65"/>
-      <c r="P65"/>
-      <c r="Q65"/>
-      <c r="R65"/>
-      <c r="S65"/>
-      <c r="T65"/>
-      <c r="U65"/>
-      <c r="V65"/>
-      <c r="W65"/>
-      <c r="X65"/>
-      <c r="Y65"/>
-      <c r="Z65"/>
-      <c r="AA65"/>
-    </row>
-    <row r="66" spans="2:27" ht="11.45" customHeight="1">
-      <c r="B66"/>
-      <c r="C66"/>
-      <c r="D66"/>
-      <c r="E66"/>
-      <c r="F66"/>
-      <c r="G66"/>
-      <c r="H66"/>
-      <c r="I66"/>
-      <c r="J66"/>
-      <c r="K66"/>
-      <c r="L66"/>
-      <c r="M66"/>
-      <c r="N66"/>
-      <c r="O66"/>
-      <c r="P66"/>
-      <c r="Q66"/>
-      <c r="R66"/>
-      <c r="S66"/>
-      <c r="T66"/>
-      <c r="U66"/>
-      <c r="V66"/>
-      <c r="W66"/>
-      <c r="X66"/>
-      <c r="Y66"/>
-      <c r="Z66"/>
-      <c r="AA66"/>
-    </row>
-    <row r="67" spans="2:27" ht="11.45" customHeight="1">
-      <c r="B67"/>
-      <c r="C67"/>
-      <c r="D67"/>
-      <c r="E67"/>
-      <c r="F67"/>
-      <c r="G67"/>
-      <c r="H67"/>
-      <c r="I67"/>
-      <c r="J67"/>
-      <c r="K67"/>
-      <c r="L67"/>
-      <c r="M67"/>
-      <c r="N67"/>
-      <c r="O67"/>
-      <c r="P67"/>
-      <c r="Q67"/>
-      <c r="R67"/>
-      <c r="S67"/>
-      <c r="T67"/>
-      <c r="U67"/>
-      <c r="V67"/>
-      <c r="W67"/>
-      <c r="X67"/>
-      <c r="Y67"/>
-      <c r="Z67"/>
-      <c r="AA67"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B9:AC15">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B9:AC10">
     <sortCondition ref="B9"/>
   </sortState>
-  <mergeCells count="10">
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="B33:C33"/>
+  <mergeCells count="2">
     <mergeCell ref="B1:O1"/>
-    <mergeCell ref="K7:Z7"/>
-    <mergeCell ref="V2:Z6"/>
     <mergeCell ref="P4:U4"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="B7:J7"/>
   </mergeCells>
+  <conditionalFormatting sqref="I40">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations disablePrompts="1" count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29" xr:uid="{7DB9EFD9-E784-464D-B93C-ABBEF7F1E8CE}">
+      <formula1>$D$43:$D$44</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33 H37" xr:uid="{9801D4AE-E571-4CBA-A92E-D326A24D3A44}">
+      <formula1>$C$43:$C$44</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.15748031496062992" right="0.19685039370078741" top="0.15748031496062992" bottom="0.15748031496062992" header="0.23622047244094491" footer="0.15748031496062992"/>
   <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId1"/>
 </worksheet>
